--- a/site/Using-Tables-in-Integrations/headings.xlsx
+++ b/site/Using-Tables-in-Integrations/headings.xlsx
@@ -463,7 +463,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Adding Tables in I ntegration</t>
+          <t>Adding Tables in Integration</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
